--- a/Generador de actas/acta_de_examen.xlsx
+++ b/Generador de actas/acta_de_examen.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection workbookPassword="C6D3" lockStructure="1"/>
+  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -57,13 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,57 +427,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMIRA YARBOUH</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17599256</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GEOGRAFÍA I</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C6D3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -491,52 +511,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMIRA YARBOUH</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17599256</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GEOGRAFÍA I</t>
         </is>
       </c>
     </row>
@@ -551,52 +595,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMIRA YARBOUH</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17599256</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GEOGRAFÍA I</t>
         </is>
       </c>
     </row>

--- a/Generador de actas/acta_de_examen.xlsx
+++ b/Generador de actas/acta_de_examen.xlsx
@@ -57,10 +57,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,78 +435,92 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>AMIRA YARBOUH</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>17599256</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>17599256</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>MMO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1°1°</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>GEOGRAFÍA I</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C6D3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -513,72 +533,85 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>AMIRA YARBOUH</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>17599256</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>17599256</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>MMO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1°1°</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>GEOGRAFÍA I</t>
         </is>
@@ -597,72 +630,85 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>AMIRA YARBOUH</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>17599256</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>17599256</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>MMO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1°1°</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>GEOGRAFÍA I</t>
         </is>

--- a/Generador de actas/acta_de_examen.xlsx
+++ b/Generador de actas/acta_de_examen.xlsx
@@ -57,16 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,89 +427,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ALUMNO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ESPACIO CURRICULAR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CONDICION 2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO 2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>AMIRA YARBOUH</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>17599256</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CARINA OLMOS</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1°1°</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>GEOGRAFÍA I</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LENGUA EXTRANJERA I (TEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CARINA PEREZ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LENGUA EXTRANJERA I (TEM)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA I (TEM)</t>
         </is>
       </c>
     </row>
@@ -531,93 +575,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>N°</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ALUMNO</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>MODALIDAD</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>CONDICION</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>CURSO</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>ESPACIO CURRICULAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>AMIRA YARBOUH</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>17599256</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>GEOGRAFÍA I</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -628,90 +588,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>N°</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ALUMNO</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CONDICION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>CURSO</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>ESPACIO CURRICULAR</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ALUMNO 1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>DNI 1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ALUMNO 2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DNI 2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>AMIRA YARBOUH</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>17599256</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>MMO</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LENGUA EXTRANJERA I (TEM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1°1°</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>REGULAR</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CARINA OLMOS</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CARINA PEREZ</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA I (TEM)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>1°1°</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>GEOGRAFÍA I</t>
-        </is>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CARINA PEREZ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Generador de actas/acta_de_examen.xlsx
+++ b/Generador de actas/acta_de_examen.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERMISOS" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEM" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,7 +27,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,23 +49,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,8 +440,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="43" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="37" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -481,90 +521,3227 @@
           <t>ESPACIO CURRICULAR 2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CONDICION 3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO 3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>CONDICION 4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO 4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>CONDICION 5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO 5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>CONDICION 6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>CURSO 6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONDICION </t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURSO </t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ESPACIO CURRICULAR 7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CARINA OLMOS</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CARRIZO CASTRO, FERNANDO CAMIL</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>48560106</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>TEM</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA I (TEM)</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>MECÁNICA</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CARINA PEREZ</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BORDON, TOBIAS ABSALÓN</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>44571729</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE PROYECTO</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MADRIGAL, GONZALO GAEL</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>50337310</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CHAYLE, MAICO MISAEL</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>50337313</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="2" t="n"/>
+      <c r="Y5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CABRERA, ANGEL JULIAN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>47969681</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>TEM</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA I (TEM)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>LENGUA Y LITERATURA I (TEM)</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
+      <c r="Y6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CHAYLE REALES, GUADALUPE DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>47722726</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="n"/>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="2" t="n"/>
+      <c r="X7" s="2" t="n"/>
+      <c r="Y7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NIEVA, LEILA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>47192485</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>HIGIENE Y PROT. AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>PROY. Y DISEÑO ELECTROMECÁNICO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>PROY. Y DISEÑO DE INST. ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>REINOSO, VICTORIA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>47035096</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA II (TEM)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GUARDIA NORMA AGOSTINA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>47192487</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y PROCESAM MECÁNICO I (TEM)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ELECTROTECNIA II (TEM)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA (TEM)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLICAC. DE LA ENERGÍA III (TEM)</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GAITAN, LARA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>49294906</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I (TEM)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CARRIZO, NAIARA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>49294911</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I (TEM)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>BARBIERI, FRANCESCO GIOVANNI</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>44570762</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y CALCULO DE ESTRUCTURAS (MMO)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS ELECTRICOS Y ELECTRÓNICOS DOMICILIARIOS (MMO)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>ACONDICIONAM. TÉRMICO - INST. DE GAS (MMO)</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n"/>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="n"/>
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VILLAGRA, JOSÉ ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>45457904</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y CALCULO DE ESTRUCTURAS (MMO)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE DIRECCIÃN (MMO)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>PROYECTO FINAL (MMO)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>PALACIOS, FABRICIO SAMUEL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>48397489</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2°2°</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II (TEM)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3°2°</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>MATEMATICA III (TEM)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="n"/>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MOYA, EMILIO GABRIEL</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>49294901</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>HISTORIA II (MMO)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CARDOSO, CANDELA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>44942699</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE PROYECTO (MMO)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CARRIZO, ERIKA MILAGROS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>50915508</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>EDUC. ARTÍSTICA: ARTES VISUALES (MMO)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II (MMO)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>QUIMICA II (MMO)</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>FORMACIÓN ETICA Y CIUDADANA II (MMO)</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2º1º</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>HISTORIA II</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AGÜERO TABORDA, FACUNDO AGUSTIN</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>49978218</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>EDUC. ARTÍSTICA: ARTES VISUALES (MMO)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2º1º</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II (MMO)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
+      <c r="T19" s="2" t="n"/>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="n"/>
+      <c r="X19" s="2" t="n"/>
+      <c r="Y19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ, JOSÈ IGNACIO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>44942665</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>HIGIENE Y PROT. AMBIENTAL (TEM)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>PROY. Y DISEÑO ELECTROMECÁNICO (TEM)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="n"/>
+      <c r="Y20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CARRIZO, ABRIL MARIANA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>45664571</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y CALCULO DE ESTRUCTURAS (MMO)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>GESTION DE OBRAS (MMO)</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="W21" s="2" t="n"/>
+      <c r="X21" s="2" t="n"/>
+      <c r="Y21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CHAILE, AIXA CASANDRA</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>46464805</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y CALCULO DE ESTRUCTURAS (MMO)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>GESTION DE OBRAS (MMO)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="W22" s="2" t="n"/>
+      <c r="X22" s="2" t="n"/>
+      <c r="Y22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>NABARRO HEREDIA, MELANI</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>44571731</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>DISEÑO Y CALCULO DE ESTRUCTURAS (MMO)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>COMPUTO Y PRESUPUESTOS (MMO)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SISMORRESISTENTE PROYECTO </t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE CONSTRUCCIONES (MMO)</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MORENO CRESPIN, SOL ELIZABETH</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>45567181</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE CONSTRUCCIONES (MMO)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE DIRECCION (MMO)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="2" t="n"/>
+      <c r="X24" s="2" t="n"/>
+      <c r="Y24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>PEÑALOZA, LUCAS LEONEL</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>48569163</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3°1°</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>HISTORIA III (TEM)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3°1°</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>GEOGRAFIA III (TEM)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="2" t="n"/>
+      <c r="X25" s="2" t="n"/>
+      <c r="Y25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SALVA, JOEL SAMIR</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>46595464</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA VI (MMO)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>INGLÉS TÉCNICO II (MMO)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>PROYECTO II (MMO)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
+      <c r="X26" s="2" t="n"/>
+      <c r="Y26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>YAPURA, TOMAS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>46595453</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS ELECTRICOS Y ELECTRÓNICOS DOMICILIARIOS (MMO)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMA SANITARIO EDILICIO (MMO)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="2" t="n"/>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CHAILE OLARTE, GABRIEL ANTONIO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>46464786</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMA SANITARIO EDILICIO (MMO)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS ELECTRICOS Y ELECTRÓNICOS DOMICILIARIOS (MMO)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="2" t="n"/>
+      <c r="X28" s="2" t="n"/>
+      <c r="Y28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CASAS, EMILCE LILIANA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>47192444</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS ELECTRICOS Y ELECTRÓNICOS DOMICILIARIOS (MMO)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMA SANITARIO EDILICIO (MMO)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n"/>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n"/>
+      <c r="W29" s="2" t="n"/>
+      <c r="X29" s="2" t="n"/>
+      <c r="Y29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ARCE, YOSELI</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>47192413</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MARCO JURÍDICO DE LOS PROC. CONSTRUCTIVOS (MMO)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMA SANITARIO EDILICIO (MMO)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS ELECTRICOS Y ELECTRÓNICOS DOMICILIARIOS (MMO)</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>PROYECTO II</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>TOPOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
+      <c r="X30" s="2" t="n"/>
+      <c r="Y30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CARRIZO, ARIADNA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>49798250</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>TECNOLOGÍA DE LOS PROCESOS (TEM)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3°1°</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO III (TEM)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="W31" s="2" t="n"/>
+      <c r="X31" s="2" t="n"/>
+      <c r="Y31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>VARAS, THIANA NANCY</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>49867427</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>3°1°</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO III (TEM)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="2" t="n"/>
+      <c r="X32" s="2" t="n"/>
+      <c r="Y32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>LAURÍA FERNANDEZ, MATIAS EZEQUIEL</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>45078947</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MECÁNICA (TEM)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6°2°</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>ELECTROTECNIA II (TEM)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TALLER DE ELECTRÓNICA </t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEGURIDAD, HIGIENE Y CONTROL AMBIENTAL </t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="2" t="n"/>
+      <c r="X33" s="2" t="n"/>
+      <c r="Y33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>OLMOS, IGNACIO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>47903558</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA IV (TEM)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÁQUINAS ELÉCTRICAS Y AUTOMATISMOS I </t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>5º1º</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA V</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="2" t="n"/>
+      <c r="X34" s="2" t="n"/>
+      <c r="Y34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SACABAS, JUAN CRUZ</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>46464880</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE CONSTRUCCIONES (MMO)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SISMORRESISTENTE DIRECCIÓN </t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SISMORRESISTENTE PROYECTO </t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="2" t="n"/>
+      <c r="X35" s="2" t="n"/>
+      <c r="Y35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CEDAN CARRIZO, BENJAMIN ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>47192482</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>MECÁNICA (TEM)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="2" t="n"/>
+      <c r="X36" s="2" t="n"/>
+      <c r="Y36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>GODOY, KEVIN ADRIAN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>47722788</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2°2°</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA II (MMO)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3°2°</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>LENGUA Y LITERATURA III (MMO)</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>3°2°</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>TIC`S (MMO)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="n"/>
+      <c r="U37" s="2" t="n"/>
+      <c r="V37" s="2" t="n"/>
+      <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
+      <c r="Y37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>PALACIOS, FACUNDO MARTIN</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>47722761</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ANALISIS MATEMATICO I (TEM)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MÁQUINAS ELÉCTRICAS Y AUTOMATISMOS I </t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="W38" s="2" t="n"/>
+      <c r="X38" s="2" t="n"/>
+      <c r="Y38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>DIAZ, EXEQUIEL NAHUM</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>47523483</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>5°1°</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MECÁNICA (TEM)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS DE MECANIZADO (TEM)</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>INST. DE CONTROL AUTOMATIZADO (TEM)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="W39" s="2" t="n"/>
+      <c r="X39" s="2" t="n"/>
+      <c r="Y39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>OLMOS, PEDRO VALENTÍN</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>49450748</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2°1°</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>EDUC. ARTÍSTICA: ARTES VISUALES (MMO)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="W40" s="2" t="n"/>
+      <c r="X40" s="2" t="n"/>
+      <c r="Y40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>RASGIDO, CARIM JON</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>47628487</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n"/>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
+      <c r="Y41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>RASGIDO, CARIM EXEQUIEL</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>47628486</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>4°1°</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLIC DE LA ENERGÍA I (TEM)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4º1º</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>MAQUINAS ELÉCTRICAS Y AUTOMATISMOS I</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
+      <c r="U42" s="2" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="W42" s="2" t="n"/>
+      <c r="X42" s="2" t="n"/>
+      <c r="Y42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ROBLEDO, ABIGAIL DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>47192424</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>6°1°</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>INST. Y APLICAC. DE LA ENERGÍA III (TEM)</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>6º1º</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS DE MECANIZADO (TEM)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIGIENE, SEGURIDAD Y CONTROL AMBIENTAL </t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>LAB. DE METROLGÍA Y CONTROL DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROY. Y DISEÑO DE INST. ELECTROMECÁNICAS </t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROY. Y DISEÑO DE INST. ELÉCTRICAS </t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGULAR </t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>7º1º</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>SISTEMAS MECÁNICOS II</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>REALES, AIXA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>43531901</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>7°1°</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SISMORRESISTENTE PROYECTO (MMO)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>BRUNO, FLORENCIA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>49764954</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>MMO</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2°2°</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>DIBUJO TÉCNICO II (MMO)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2°2°</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>GEOGRAFÍA II (MMO)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
+      <c r="Y45" s="2" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C6D3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +3755,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -588,120 +3765,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ESPACIO CURRICULAR</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>CURSO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>MODALIDAD</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CONDICION</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ALUMNO 1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>DNI 1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ALUMNO 2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DNI 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LENGUA EXTRANJERA I (TEM)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CARINA OLMOS</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CARINA PEREZ</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LENGUA Y LITERATURA I (TEM)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1°1°</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CARINA PEREZ</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <sheetData/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="C6D3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>